--- a/data/trans_dic/P16-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,58; 46,97</t>
+          <t>37,68; 46,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,64; 54,39</t>
+          <t>44,31; 54,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,84; 58,09</t>
+          <t>47,25; 57,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,29; 60,36</t>
+          <t>51,19; 60,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,16; 59,42</t>
+          <t>48,57; 59,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,16; 66,5</t>
+          <t>55,26; 67,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,03; 60,8</t>
+          <t>49,54; 60,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,63; 62,72</t>
+          <t>54,44; 62,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,36; 50,84</t>
+          <t>43,41; 50,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,03; 58,07</t>
+          <t>50,34; 57,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,17; 57,78</t>
+          <t>50,29; 57,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,96; 60,26</t>
+          <t>53,63; 59,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,35; 45,19</t>
+          <t>34,29; 45,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,53; 55,44</t>
+          <t>45,01; 55,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,97; 55,5</t>
+          <t>44,76; 55,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,53; 59,81</t>
+          <t>49,73; 59,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,41; 58,81</t>
+          <t>48,36; 58,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,59; 68,82</t>
+          <t>58,27; 69,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,46; 61,4</t>
+          <t>51,45; 61,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,04; 62,67</t>
+          <t>53,33; 62,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,71; 50,18</t>
+          <t>42,86; 50,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,18; 60,17</t>
+          <t>51,91; 59,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,8; 56,87</t>
+          <t>49,65; 56,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,85; 59,69</t>
+          <t>52,89; 59,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,17</t>
+          <t>36,41; 44,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,57; 59,59</t>
+          <t>51,49; 59,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,91; 60,33</t>
+          <t>51,42; 60,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 59,55</t>
+          <t>14,94; 59,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 61,47</t>
+          <t>46,2; 62,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,61; 72,21</t>
+          <t>61,06; 73,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,17; 76,65</t>
+          <t>61,93; 76,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,76; 78,89</t>
+          <t>67,7; 78,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,13; 47,83</t>
+          <t>40,42; 47,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,31; 62,49</t>
+          <t>55,85; 62,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,49; 63,02</t>
+          <t>55,54; 63,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 63,82</t>
+          <t>20,71; 63,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 48,04</t>
+          <t>42,45; 48,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,56; 55,62</t>
+          <t>49,71; 55,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,1; 54,89</t>
+          <t>48,95; 54,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,87; 58,62</t>
+          <t>51,61; 58,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,37; 57,58</t>
+          <t>50,17; 57,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,97; 71,02</t>
+          <t>64,1; 71,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,21; 61,79</t>
+          <t>54,78; 61,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,72; 84,43</t>
+          <t>61,64; 82,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,22; 50,9</t>
+          <t>46,01; 50,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,34; 60,99</t>
+          <t>56,17; 60,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,31; 56,8</t>
+          <t>52,28; 56,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,38; 72,87</t>
+          <t>57,6; 74,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,55; 45,93</t>
+          <t>35,64; 46,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,25; 54,88</t>
+          <t>46,05; 54,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,04; 54,76</t>
+          <t>46,5; 54,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,51; 60,23</t>
+          <t>50,41; 60,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,24; 65,5</t>
+          <t>57,29; 66,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 79,08</t>
+          <t>72,7; 79,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,69; 75,45</t>
+          <t>68,73; 75,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,77; 76,89</t>
+          <t>62,79; 77,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,19; 56,82</t>
+          <t>50,39; 56,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,96; 68,35</t>
+          <t>62,67; 68,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,49; 65,0</t>
+          <t>59,67; 64,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,87; 70,55</t>
+          <t>60,36; 70,84</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,59; 23,68</t>
+          <t>14,67; 23,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,74; 36,76</t>
+          <t>25,34; 36,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,55; 29,78</t>
+          <t>19,64; 29,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 37,77</t>
+          <t>18,04; 38,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,35; 65,88</t>
+          <t>60,4; 65,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,89; 76,26</t>
+          <t>70,68; 76,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,04; 72,83</t>
+          <t>67,04; 72,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,4; 66,43</t>
+          <t>59,06; 66,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,01; 56,82</t>
+          <t>52,32; 57,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62,4; 67,57</t>
+          <t>62,64; 67,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,67; 63,34</t>
+          <t>57,56; 63,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 57,87</t>
+          <t>49,97; 57,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,71; 42,36</t>
+          <t>38,89; 42,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,7; 52,38</t>
+          <t>48,47; 52,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,12; 51,64</t>
+          <t>48,1; 51,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,02; 53,97</t>
+          <t>39,35; 53,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,78; 60,25</t>
+          <t>56,99; 60,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,66; 71,84</t>
+          <t>68,62; 71,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,15; 66,26</t>
+          <t>62,99; 66,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,25; 72,88</t>
+          <t>63,53; 72,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,6; 50,98</t>
+          <t>48,28; 50,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,27; 61,62</t>
+          <t>59,29; 61,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56,33; 58,86</t>
+          <t>56,33; 58,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,68; 61,81</t>
+          <t>51,71; 61,61</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>178051; 222538</t>
+          <t>178527; 221417</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195164; 237810</t>
+          <t>193716; 238059</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205276; 249260</t>
+          <t>202735; 246588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259113; 304938</t>
+          <t>258632; 306135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>147691; 182218</t>
+          <t>148944; 181273</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>173438; 209111</t>
+          <t>173755; 212514</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>173629; 210995</t>
+          <t>171919; 209895</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>244450; 280664</t>
+          <t>243588; 280833</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>338369; 396808</t>
+          <t>338789; 392345</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>376091; 436472</t>
+          <t>378398; 435506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>389423; 448444</t>
+          <t>390298; 448534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>514053; 574050</t>
+          <t>510961; 570384</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126058; 165814</t>
+          <t>125838; 165678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>185690; 231213</t>
+          <t>187692; 230020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169651; 209368</t>
+          <t>168857; 207977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>223967; 270470</t>
+          <t>224902; 270446</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>180012; 218706</t>
+          <t>179836; 218271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194110; 231930</t>
+          <t>196399; 233037</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>187861; 228589</t>
+          <t>191529; 229322</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>206727; 239747</t>
+          <t>204016; 238338</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>315544; 370731</t>
+          <t>316640; 373516</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>393430; 453740</t>
+          <t>391447; 451297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>373258; 426276</t>
+          <t>372149; 426456</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>441204; 498312</t>
+          <t>441505; 495835</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>198500; 245012</t>
+          <t>197499; 243896</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>324029; 374431</t>
+          <t>323546; 375153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>270930; 314845</t>
+          <t>268355; 313796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91394; 397934</t>
+          <t>99811; 398979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77525; 103130</t>
+          <t>77511; 104092</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155064; 187851</t>
+          <t>158840; 190931</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>104944; 127329</t>
+          <t>102877; 126736</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113103; 131679</t>
+          <t>113006; 131286</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>284974; 339679</t>
+          <t>287037; 340412</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491437; 555223</t>
+          <t>496238; 552714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>381818; 433616</t>
+          <t>382117; 434771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>159448; 533030</t>
+          <t>173002; 527722</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>523797; 594864</t>
+          <t>525688; 596246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>573974; 644205</t>
+          <t>575729; 647852</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>564514; 631064</t>
+          <t>562724; 629031</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536747; 606651</t>
+          <t>534021; 607613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>359804; 411265</t>
+          <t>358383; 409749</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>490419; 544496</t>
+          <t>491432; 544875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>455994; 510327</t>
+          <t>452398; 510758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>603660; 825807</t>
+          <t>602884; 810858</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>902447; 993931</t>
+          <t>898425; 988708</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1084350; 1173932</t>
+          <t>1081119; 1172737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033348; 1122081</t>
+          <t>1032865; 1124031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1154967; 1466873</t>
+          <t>1159505; 1500961</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124278; 160556</t>
+          <t>124564; 160805</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>236147; 280210</t>
+          <t>235142; 280159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>285803; 339909</t>
+          <t>288633; 336328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239956; 286118</t>
+          <t>239460; 289631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>325557; 372529</t>
+          <t>325828; 375596</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>550943; 601427</t>
+          <t>552903; 602391</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>507124; 557039</t>
+          <t>507427; 554568</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>526642; 645143</t>
+          <t>526781; 650755</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>460909; 521806</t>
+          <t>462713; 521901</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>800222; 868742</t>
+          <t>796583; 866179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>808376; 883328</t>
+          <t>810891; 882909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>786709; 927061</t>
+          <t>793144; 930923</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43522; 70604</t>
+          <t>43738; 70631</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65760; 97723</t>
+          <t>67359; 96369</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56128; 85518</t>
+          <t>56391; 85687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42219; 90843</t>
+          <t>43396; 92439</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>753653; 822695</t>
+          <t>754251; 821253</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>785811; 845289</t>
+          <t>783407; 843103</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>725377; 788065</t>
+          <t>725437; 785131</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>451494; 504946</t>
+          <t>448983; 503036</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>804545; 878940</t>
+          <t>809370; 882133</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>857568; 928636</t>
+          <t>860891; 930254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>789546; 867166</t>
+          <t>788118; 862951</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>500056; 579115</t>
+          <t>500016; 577402</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1265605; 1384678</t>
+          <t>1271302; 1381394</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1664151; 1789781</t>
+          <t>1656346; 1781671</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1629271; 1748449</t>
+          <t>1628661; 1745263</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1283454; 1822196</t>
+          <t>1328503; 1820298</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1918162; 2035458</t>
+          <t>1925145; 2038986</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2435455; 2548377</t>
+          <t>2434171; 2545599</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2230070; 2339965</t>
+          <t>2224641; 2344618</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2260529; 2604887</t>
+          <t>2270639; 2585264</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3230812; 3388591</t>
+          <t>3209430; 3383241</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4128087; 4291446</t>
+          <t>4129316; 4293310</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3896300; 4071503</t>
+          <t>3896812; 4056023</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3591701; 4295853</t>
+          <t>3594169; 4281786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,68; 46,73</t>
+          <t>37,98; 47,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,31; 54,45</t>
+          <t>44,2; 54,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,25; 57,47</t>
+          <t>47,91; 58,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,19; 60,6</t>
+          <t>50,95; 59,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,57; 59,11</t>
+          <t>48,13; 59,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,26; 67,58</t>
+          <t>55,39; 66,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,54; 60,48</t>
+          <t>50,28; 60,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,44; 62,76</t>
+          <t>53,76; 61,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,41; 50,27</t>
+          <t>43,46; 50,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,34; 57,94</t>
+          <t>50,41; 57,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,29; 57,79</t>
+          <t>49,97; 57,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,63; 59,87</t>
+          <t>53,4; 59,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,29; 45,15</t>
+          <t>34,77; 44,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,01; 55,16</t>
+          <t>44,61; 55,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,76; 55,13</t>
+          <t>44,66; 55,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,73; 59,81</t>
+          <t>48,64; 58,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,36; 58,7</t>
+          <t>48,43; 58,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,27; 69,14</t>
+          <t>57,86; 69,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,45; 61,6</t>
+          <t>51,06; 61,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,33; 62,3</t>
+          <t>53,96; 62,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,86; 50,56</t>
+          <t>42,7; 50,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,91; 59,85</t>
+          <t>52,31; 60,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,65; 56,9</t>
+          <t>49,58; 56,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,89; 59,4</t>
+          <t>52,5; 58,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>61,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,41; 44,97</t>
+          <t>36,64; 45,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,49; 59,71</t>
+          <t>51,48; 59,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,42; 60,12</t>
+          <t>51,13; 59,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 59,7</t>
+          <t>52,61; 61,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,2; 62,04</t>
+          <t>46,86; 61,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,06; 73,4</t>
+          <t>61,12; 73,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,93; 76,29</t>
+          <t>62,39; 76,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,7; 78,66</t>
+          <t>67,03; 77,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,42; 47,93</t>
+          <t>40,06; 47,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,85; 62,21</t>
+          <t>55,58; 62,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,54; 63,19</t>
+          <t>55,19; 62,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 63,19</t>
+          <t>58,0; 65,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,45; 48,15</t>
+          <t>42,22; 47,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,94</t>
+          <t>49,63; 55,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,95; 54,72</t>
+          <t>49,13; 54,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,61; 58,72</t>
+          <t>52,15; 58,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,17; 57,36</t>
+          <t>50,0; 57,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,1; 71,07</t>
+          <t>63,99; 71,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,78; 61,84</t>
+          <t>54,77; 61,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,64; 82,9</t>
+          <t>59,99; 65,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,01; 50,63</t>
+          <t>46,02; 50,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,17; 60,93</t>
+          <t>56,13; 61,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,28; 56,9</t>
+          <t>52,48; 57,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,6; 74,57</t>
+          <t>56,4; 60,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,64; 46,01</t>
+          <t>35,53; 46,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,05; 54,87</t>
+          <t>45,77; 54,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,5; 54,18</t>
+          <t>46,69; 54,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,41; 60,97</t>
+          <t>45,88; 54,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,29; 66,04</t>
+          <t>57,54; 65,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,7; 79,21</t>
+          <t>72,56; 78,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 75,12</t>
+          <t>68,81; 75,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,79; 77,56</t>
+          <t>66,5; 72,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,39; 56,83</t>
+          <t>50,62; 57,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,67; 68,14</t>
+          <t>62,95; 68,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,67; 64,97</t>
+          <t>59,96; 64,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,36; 70,84</t>
+          <t>59,15; 64,3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 23,69</t>
+          <t>14,28; 22,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,34; 36,25</t>
+          <t>25,29; 36,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 29,84</t>
+          <t>19,5; 30,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,04; 38,43</t>
+          <t>17,32; 35,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,4; 65,77</t>
+          <t>60,44; 65,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,68; 76,06</t>
+          <t>70,77; 76,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,04; 72,56</t>
+          <t>66,78; 72,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,06; 66,18</t>
+          <t>58,79; 65,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,32; 57,02</t>
+          <t>51,93; 57,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62,64; 67,69</t>
+          <t>62,44; 67,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,56; 63,03</t>
+          <t>57,66; 63,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 57,7</t>
+          <t>50,7; 57,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,89; 42,26</t>
+          <t>38,86; 42,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,47; 52,14</t>
+          <t>48,62; 52,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,1; 51,55</t>
+          <t>47,99; 51,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,35; 53,92</t>
+          <t>50,63; 54,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,99; 60,36</t>
+          <t>56,89; 60,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,62; 71,76</t>
+          <t>68,64; 71,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,99; 66,39</t>
+          <t>63,18; 66,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,53; 72,33</t>
+          <t>62,08; 64,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,28; 50,9</t>
+          <t>48,53; 51,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,29; 61,65</t>
+          <t>59,28; 61,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56,33; 58,64</t>
+          <t>56,24; 58,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,71; 61,61</t>
+          <t>56,84; 59,33</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>303119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>261879</t>
+          <t>282667</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>542954</t>
+          <t>585786</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>178527; 221417</t>
+          <t>179935; 223485</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>193716; 238059</t>
+          <t>193236; 236952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>202735; 246588</t>
+          <t>205582; 249148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258632; 306135</t>
+          <t>280567; 326579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>148944; 181273</t>
+          <t>147605; 183792</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>173755; 212514</t>
+          <t>174164; 209488</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>171919; 209895</t>
+          <t>174482; 210599</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>243588; 280833</t>
+          <t>262557; 300732</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>338789; 392345</t>
+          <t>339214; 396333</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>378398; 435506</t>
+          <t>378885; 435295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>390298; 448534</t>
+          <t>387811; 447875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>510961; 570384</t>
+          <t>554838; 617665</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247223</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>222928</t>
+          <t>244331</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>470151</t>
+          <t>504871</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125838; 165678</t>
+          <t>127575; 164760</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187692; 230020</t>
+          <t>186044; 230920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168857; 207977</t>
+          <t>168465; 208561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224902; 270446</t>
+          <t>235049; 283122</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>179836; 218271</t>
+          <t>180113; 216061</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196399; 233037</t>
+          <t>195001; 233195</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>191529; 229322</t>
+          <t>190083; 229670</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>204016; 238338</t>
+          <t>228338; 263617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>316640; 373516</t>
+          <t>315459; 370776</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>391447; 451297</t>
+          <t>394411; 453908</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>372149; 426456</t>
+          <t>371576; 425069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>441505; 495835</t>
+          <t>475871; 534603</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245448</t>
+          <t>269607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>122554</t>
+          <t>136189</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>368002</t>
+          <t>405797</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>197499; 243896</t>
+          <t>198731; 246192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>323546; 375153</t>
+          <t>323433; 375223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>268355; 313796</t>
+          <t>266850; 312616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99811; 398979</t>
+          <t>248112; 290779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77511; 104092</t>
+          <t>78630; 103730</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>158840; 190931</t>
+          <t>158992; 190604</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>102877; 126736</t>
+          <t>103645; 127471</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113006; 131286</t>
+          <t>125674; 146177</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>287037; 340412</t>
+          <t>284505; 335484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>496238; 552714</t>
+          <t>493808; 551604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>382117; 434771</t>
+          <t>379696; 433014</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>173002; 527722</t>
+          <t>382301; 430848</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570263</t>
+          <t>626825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>690226</t>
+          <t>540595</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1260489</t>
+          <t>1167420</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>525688; 596246</t>
+          <t>522767; 592225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>575729; 647852</t>
+          <t>574781; 646509</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>562724; 629031</t>
+          <t>564787; 631103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534021; 607613</t>
+          <t>590269; 665278</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>358383; 409749</t>
+          <t>357155; 410173</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>491432; 544875</t>
+          <t>490578; 546388</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>452398; 510758</t>
+          <t>452363; 509917</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>602884; 810858</t>
+          <t>516627; 565707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>898425; 988708</t>
+          <t>898526; 985912</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1081119; 1172737</t>
+          <t>1080318; 1174246</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1032865; 1124031</t>
+          <t>1036689; 1126710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1159505; 1500961</t>
+          <t>1124098; 1211099</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263456</t>
+          <t>287128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>596349</t>
+          <t>576864</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>859804</t>
+          <t>863992</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124564; 160805</t>
+          <t>124173; 161524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>235142; 280159</t>
+          <t>233710; 279380</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>288633; 336328</t>
+          <t>289779; 337283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239460; 289631</t>
+          <t>260576; 311783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>325828; 375596</t>
+          <t>327261; 373600</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>552903; 602391</t>
+          <t>551846; 599801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>507427; 554568</t>
+          <t>508007; 554522</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>526781; 650755</t>
+          <t>552039; 600281</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>462713; 521901</t>
+          <t>464800; 526732</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>796583; 866179</t>
+          <t>800165; 865036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>810891; 882909</t>
+          <t>814827; 883233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>793144; 930923</t>
+          <t>827018; 898941</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63832</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>477623</t>
+          <t>524448</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>541454</t>
+          <t>584856</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43738; 70631</t>
+          <t>42572; 68011</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67359; 96369</t>
+          <t>67226; 97117</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56391; 85687</t>
+          <t>56004; 86633</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43396; 92439</t>
+          <t>41077; 83462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>754251; 821253</t>
+          <t>754734; 821388</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>783407; 843103</t>
+          <t>784485; 844001</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>725437; 785131</t>
+          <t>722628; 785532</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>448983; 503036</t>
+          <t>495625; 555507</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>809370; 882133</t>
+          <t>803286; 882054</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>860891; 930254</t>
+          <t>858146; 931313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>788118; 862951</t>
+          <t>789511; 864974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>500016; 577402</t>
+          <t>547722; 626455</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1671297</t>
+          <t>1807626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2371557</t>
+          <t>2305095</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4042855</t>
+          <t>4112721</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1271302; 1381394</t>
+          <t>1270497; 1384179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1656346; 1781671</t>
+          <t>1661565; 1777914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1628661; 1745263</t>
+          <t>1624753; 1743172</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1328503; 1820298</t>
+          <t>1743035; 1872077</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1925145; 2038986</t>
+          <t>1921799; 2033280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2434171; 2545599</t>
+          <t>2434869; 2546009</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2224641; 2344618</t>
+          <t>2231122; 2346508</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2270639; 2585264</t>
+          <t>2255486; 2358297</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3209430; 3383241</t>
+          <t>3225686; 3393279</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4129316; 4293310</t>
+          <t>4128617; 4294477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3896812; 4056023</t>
+          <t>3890639; 4057488</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3594169; 4281786</t>
+          <t>4021621; 4198093</t>
         </is>
       </c>
     </row>
